--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N39_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N39_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>44.68802281187568</v>
+        <v>7.261803706929798</v>
       </c>
       <c r="D2" t="n">
-        <v>44.11997419045459</v>
+        <v>7.169495805948872</v>
       </c>
       <c r="E2" t="n">
-        <v>10.69125108393161</v>
+        <v>1.737328301138886</v>
       </c>
       <c r="F2" t="n">
-        <v>13.05731482785532</v>
+        <v>2.121813659526489</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>42.74206759785359</v>
+        <v>6.945585984651209</v>
       </c>
       <c r="D3" t="n">
-        <v>41.89383354757665</v>
+        <v>6.807747951481206</v>
       </c>
       <c r="E3" t="n">
-        <v>10.69125108393161</v>
+        <v>1.737328301138886</v>
       </c>
       <c r="F3" t="n">
-        <v>13.05731482785532</v>
+        <v>2.121813659526489</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.13755831858268</v>
+        <v>4.897353226769686</v>
       </c>
       <c r="D4" t="n">
-        <v>25.15400930324583</v>
+        <v>4.087526511777448</v>
       </c>
       <c r="E4" t="n">
-        <v>10.69125108393161</v>
+        <v>1.737328301138886</v>
       </c>
       <c r="F4" t="n">
-        <v>13.05731482785532</v>
+        <v>2.121813659526489</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>23.05160196049511</v>
+        <v>3.745885318580455</v>
       </c>
       <c r="D5" t="n">
-        <v>22.85467236263155</v>
+        <v>3.713884258927627</v>
       </c>
       <c r="E5" t="n">
-        <v>10.69125108393161</v>
+        <v>1.737328301138886</v>
       </c>
       <c r="F5" t="n">
-        <v>13.05731482785532</v>
+        <v>2.121813659526489</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.45054615262973</v>
+        <v>4.298213749802331</v>
       </c>
       <c r="D6" t="n">
-        <v>27.57503431296344</v>
+        <v>4.480943075856559</v>
       </c>
       <c r="E6" t="n">
-        <v>10.69125108393161</v>
+        <v>1.737328301138886</v>
       </c>
       <c r="F6" t="n">
-        <v>13.05731482785532</v>
+        <v>2.121813659526489</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>39.46579239817047</v>
+        <v>6.413191264702702</v>
       </c>
       <c r="D7" t="n">
-        <v>50.53645559152884</v>
+        <v>8.212174033623437</v>
       </c>
       <c r="E7" t="n">
-        <v>10.69125108393161</v>
+        <v>1.737328301138886</v>
       </c>
       <c r="F7" t="n">
-        <v>13.05731482785532</v>
+        <v>2.121813659526489</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>33.57527431219123</v>
+        <v>5.455982075731074</v>
       </c>
       <c r="D8" t="n">
-        <v>45.89018412804269</v>
+        <v>7.457154920806937</v>
       </c>
       <c r="E8" t="n">
-        <v>10.69125108393161</v>
+        <v>1.737328301138886</v>
       </c>
       <c r="F8" t="n">
-        <v>13.05731482785532</v>
+        <v>2.121813659526489</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>10.33571081209042</v>
+        <v>1.679553006964693</v>
       </c>
       <c r="D9" t="n">
-        <v>10.7198462904661</v>
+        <v>1.741975022200742</v>
       </c>
       <c r="E9" t="n">
-        <v>10.69125108393161</v>
+        <v>1.737328301138886</v>
       </c>
       <c r="F9" t="n">
-        <v>13.05731482785532</v>
+        <v>2.121813659526489</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
